--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3289-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3289-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF59C9C0-156B-4CCC-931A-DE3D48E78DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B96BDF5-0CBB-4CB0-AA7E-6EF8A222B502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{B9BDF7DD-5159-407F-8633-2C4E8C807C38}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{F17CBE12-A5EE-4895-B278-DA02E8C08B0E}"/>
   </bookViews>
   <sheets>
     <sheet name="3289-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1594,28 +1594,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5CBB322-B50B-4164-8FAF-9EE647F57F90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F132EC-8A9E-49EB-BEE4-F21E885D1E22}">
   <dimension ref="A1:X53"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1649,7 +1649,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1685,7 +1685,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1805,7 +1805,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1913,7 +1913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="49">
         <v>2024</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>29</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
         <v>29</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
         <v>29</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="51">
         <v>2023</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="49">
         <v>2022</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>29</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>29</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="18" t="s">
         <v>29</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
         <v>29</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
         <v>29</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="51">
         <v>2021</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="49">
         <v>2020</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>7.68</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
         <v>29</v>
       </c>
@@ -3901,7 +3901,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="18" t="s">
         <v>29</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="18" t="s">
         <v>29</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="51">
         <v>2019</v>
       </c>
@@ -4121,7 +4121,7 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="49">
         <v>2018</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="51">
         <v>2017</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="49">
         <v>2016</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="51">
         <v>2015</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="49">
         <v>2014</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="51">
         <v>2013</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="49">
         <v>2012</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="51">
         <v>2011</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="49">
         <v>2010</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="51">
         <v>2009</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="49">
         <v>2008</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>9.8800000000000008</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="51">
         <v>2007</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="49">
         <v>2006</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>7.42</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="51">
         <v>2005</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>5.85</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="49">
         <v>2004</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="51">
         <v>2003</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="49" t="s">
         <v>69</v>
       </c>
